--- a/artfynd/A 43272-2024 artfynd.xlsx
+++ b/artfynd/A 43272-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74440631</v>
       </c>
       <c r="B2" t="n">
-        <v>103427</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547085.7289218772</v>
+        <v>547086</v>
       </c>
       <c r="R2" t="n">
-        <v>6375103.132333288</v>
+        <v>6375103</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -744,19 +739,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 43272-2024 artfynd.xlsx
+++ b/artfynd/A 43272-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74440631</v>
       </c>
       <c r="B2" t="n">
-        <v>105806</v>
+        <v>105815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43272-2024 artfynd.xlsx
+++ b/artfynd/A 43272-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74440631</v>
       </c>
       <c r="B2" t="n">
-        <v>105815</v>
+        <v>105820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43272-2024 artfynd.xlsx
+++ b/artfynd/A 43272-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74440631</v>
       </c>
       <c r="B2" t="n">
-        <v>105820</v>
+        <v>105848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43272-2024 artfynd.xlsx
+++ b/artfynd/A 43272-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74440631</v>
       </c>
       <c r="B2" t="n">
-        <v>105848</v>
+        <v>105854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43272-2024 artfynd.xlsx
+++ b/artfynd/A 43272-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74440631</v>
       </c>
       <c r="B2" t="n">
-        <v>105854</v>
+        <v>105861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43272-2024 artfynd.xlsx
+++ b/artfynd/A 43272-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74440631</v>
       </c>
       <c r="B2" t="n">
-        <v>105861</v>
+        <v>105865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43272-2024 artfynd.xlsx
+++ b/artfynd/A 43272-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74440631</v>
       </c>
       <c r="B2" t="n">
-        <v>105865</v>
+        <v>105872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43272-2024 artfynd.xlsx
+++ b/artfynd/A 43272-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74440631</v>
       </c>
       <c r="B2" t="n">
-        <v>105875</v>
+        <v>105880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43272-2024 artfynd.xlsx
+++ b/artfynd/A 43272-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74440631</v>
       </c>
       <c r="B2" t="n">
-        <v>105880</v>
+        <v>105888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43272-2024 artfynd.xlsx
+++ b/artfynd/A 43272-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74440631</v>
       </c>
       <c r="B2" t="n">
-        <v>105888</v>
+        <v>105898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43272-2024 artfynd.xlsx
+++ b/artfynd/A 43272-2024 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>74440631</v>
       </c>
       <c r="B2" t="n">
-        <v>105898</v>
+        <v>106413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
